--- a/p6_deployment/data/usa/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:BN25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,102 +520,270 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>interceptions_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>interceptions_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away_rival_team</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COgk2UVd</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45469.85416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bensalah n 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">beirne stadium
-  pawtucket  ri </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5252</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3481</v>
-      </c>
+        <v>22000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>3</v>
       </c>
@@ -624,186 +792,4268 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EabuZlYo</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MRumD0sn</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>10</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22</v>
       </c>
       <c r="R2" t="n">
         <v>11</v>
       </c>
-      <c r="S2" t="n">
-        <v>13</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>n9nYS6gm</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>U31kqHhr</t>
-        </is>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>167</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1671</v>
       </c>
       <c r="W2" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1673</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
         <v>2024</v>
       </c>
-      <c r="AA2" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>178.4</v>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>29.36363636363636</v>
       </c>
       <c r="AD2" t="n">
-        <v>56</v>
+        <v>182.2727272727273</v>
       </c>
       <c r="AE2" t="n">
-        <v>270000</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AF2" t="n">
-        <v>65.2</v>
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3952272.727272727</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>74.18181818181819</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1785500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>23.82608695652174</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>177.8260869565217</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>66.91304347826087</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2334782.608695652</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73.91304347826087</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>22.1304347826087</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>60.1304347826087</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>881956.5217391305</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>68.91304347826087</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>189</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>58</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>179</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>118</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bL57wogd</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45469.83333333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ndiaye a 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyworth stadium
-  hamtramck  mi </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7933</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6244</v>
-      </c>
+        <v>25218</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>64</v>
+      </c>
+      <c r="L3" t="n">
+        <v>36</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>167</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>178.5454545454545</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2979545.454545455</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>64.81818181818181</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1083636.363636364</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26.17391304347826</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>180.3478260869565</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>66.65217391304348</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1332826.086956522</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>69.39130434782609</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>23.42857142857143</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>60.71428571428572</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>707142.8571428572</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>67.71428571428571</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stanford stadium
+  stanford  ca </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>50424</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40844</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>58</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>167</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2637000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>179.2222222222222</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2897222.222222222</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1585000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23.36363636363636</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>178.7727272727273</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3439772.727272727</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>125</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>134</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>175</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>52</v>
+      </c>
+      <c r="L5" t="n">
+        <v>48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>17</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>167</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2216666.666666667</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2245454.545454545</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.72727272727273</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>177.95</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2944250</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>181.5416666666667</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1533125</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>69.41666666666667</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>343</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>9275000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24662</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>167</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2332500</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23.73684210526316</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>179</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>64.89473684210526</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1530263.157894737</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>70.52631578947368</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20.71428571428572</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>57.71428571428572</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>137</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>137</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>51</v>
+      </c>
+      <c r="L7" t="n">
+        <v>49</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>167</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>26.54545454545455</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1529545.454545455</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3281363.636363636</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.45454545454545</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1958000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>24.26086956521739</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.3913043478261</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>61.8695652173913</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1705000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>67.1304347826087</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>173.3333333333333</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>405</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>25575000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>452</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>330</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8155000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15321</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>66</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>167</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1959545.454545455</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1932500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>178.7619047619048</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.095238095238095</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>62.38095238095238</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1095952.380952381</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>68.38095238095238</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>26.1875</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>63.6875</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1008437.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>68.125</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>175.3333333333333</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>195</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>211</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>198</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2275000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30109</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>52</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>167</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3286363.636363636</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>70.90909090909091</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4382500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>182.4736842105263</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>62.63157894736842</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>636315.7894736842</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>64.36842105263158</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>22.47368421052632</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>186.4736842105263</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>64.31578947368421</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1206578.947368421</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>72.36842105263158</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>392</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>411</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>385</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>71125000</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18722</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>51</v>
+      </c>
+      <c r="L10" t="n">
+        <v>49</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>19</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>167</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1251000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2372500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>178.7619047619048</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>62.38095238095238</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>764285.7142857143</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>66.95238095238095</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>29.70588235294118</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>179.0588235294118</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>65.35294117647059</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>762352.9411764706</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>65.82352941176471</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>200</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>208</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42568</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>13</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5208181.818181818</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>3260000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1089285.714285714</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>70.0952380952381</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>179.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1546000</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>176</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>209</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>218</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>331</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>5465000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19619</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>167</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>178.2727272727273</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1409090.909090909</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2577777.777777778</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>74.22222222222223</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>180.7894736842105</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>66.36842105263158</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1696842.105263158</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>72.31578947368421</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>180.5454545454545</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>64.90909090909091</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2269090.909090909</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>330</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5850000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>350</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>351</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>12675000</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25004</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>58</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>167</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1363888.888888889</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>181</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>68.72727272727273</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3790909.090909091</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>26.73913043478261</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>180.8260869565217</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>66.39130434782609</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1115217.391304348</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>70.39130434782609</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1323750</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>143</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>146</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>37</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>186</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>63</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18315</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>23</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>167</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>22.36363636363636</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>180.9090909090909</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1524545.454545455</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1124000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3894500</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>22.81818181818182</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>61.45454545454545</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>235</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>287</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>375</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>6375000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>54</v>
+      </c>
+      <c r="L15" t="n">
+        <v>46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>167</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>23.44444444444444</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1577222.222222222</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2348500</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>21.85714285714286</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>182.2857142857143</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>62.35714285714285</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1065714.285714286</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>70.64285714285714</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.238095238095238</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>62.47619047619047</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2752857.142857143</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>68.47619047619048</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>58</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>375000</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>388</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8565000</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hassan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9249</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>167</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cashman field
+  las vegas  nv </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1893</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>52</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="n">
+        <v>13</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>167</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.95833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>51</v>
+      </c>
+      <c r="L18" t="n">
+        <v>49</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>167</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.91666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8023</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>167</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.91666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corrigan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota field
+  san antonio  tx </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6625</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>68</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32</v>
+      </c>
+      <c r="M20" t="n">
+        <v>17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>15</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>167</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">encarnacion j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>51</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>167</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arroyo l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segra field
+  leesburg  va </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3076</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>44</v>
+      </c>
+      <c r="L22" t="n">
+        <v>56</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="n">
+        <v>17</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>167</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45472.83333333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nichols a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riccardo silva stadium
+  miami  fl </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1077</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>dAoaDOc7</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>rysqEtSu</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L3" t="n">
-        <v>49</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="K23" t="n">
+        <v>42</v>
+      </c>
+      <c r="L23" t="n">
+        <v>58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>16</v>
+      </c>
+      <c r="R23" t="n">
+        <v>12</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>167</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45471.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheer j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">autozone park
+  memphis  tn </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2775</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>43</v>
+      </c>
+      <c r="L24" t="n">
+        <v>57</v>
+      </c>
+      <c r="M24" t="n">
         <v>15</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>11</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>14</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>167</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z24" t="n">
         <v>7</v>
       </c>
-      <c r="Q3" t="n">
-        <v>11</v>
-      </c>
-      <c r="R3" t="n">
-        <v>13</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>lKNscApp</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>v7f8zS64</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flores g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3876</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>70</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30</v>
+      </c>
+      <c r="M25" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>14</v>
+      </c>
+      <c r="R25" t="n">
+        <v>12</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>167</v>
       </c>
-      <c r="X3" t="n">
+      <c r="V25" t="n">
         <v>1673</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="W25" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="X25" t="n">
         <v>2024</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/usa/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN16"/>
+  <dimension ref="A1:BL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,210 +550,200 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_home</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_away</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_away</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_int_rep_player_miss_home</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_val_player_miss_home</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_val_player_miss_away</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
@@ -762,78 +752,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>08pcD25G</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45490.98958333334</v>
+        <v>45493.98958333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22000</v>
+        <v>27000</v>
       </c>
       <c r="F2" t="n">
-        <v>22163</v>
+        <v>23568</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -849,203 +839,201 @@
         <v>2024</v>
       </c>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>177.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.6</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>181.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.4</v>
+        <v>3825000</v>
       </c>
       <c r="AF2" t="n">
-        <v>72.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>4560000</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AH2" t="n">
-        <v>75.8</v>
+        <v>177.5454545454545</v>
       </c>
       <c r="AI2" t="n">
-        <v>25.5</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>180.8</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>2902272.727272727</v>
       </c>
       <c r="AL2" t="n">
-        <v>66.59999999999999</v>
+        <v>71.81818181818181</v>
       </c>
       <c r="AM2" t="n">
-        <v>1592500</v>
+        <v>23.3125</v>
       </c>
       <c r="AN2" t="n">
-        <v>71.8</v>
+        <v>181</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.35294117647059</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>181.1176470588235</v>
+        <v>64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1470312.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>66.70588235294117</v>
+        <v>70.4375</v>
       </c>
       <c r="AS2" t="n">
-        <v>1464705.882352941</v>
+        <v>26.08695652173913</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.82352941176471</v>
+        <v>181.9565217391304</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.83333333333333</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>178.6666666666667</v>
+        <v>67.21739130434783</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1379565.217391304</v>
       </c>
       <c r="AX2" t="n">
-        <v>64.33333333333333</v>
+        <v>69.65217391304348</v>
       </c>
       <c r="AY2" t="n">
-        <v>855000</v>
+        <v>30</v>
       </c>
       <c r="AZ2" t="n">
-        <v>67.66666666666667</v>
+        <v>175</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>181.3333333333333</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>2900000</v>
       </c>
       <c r="BE2" t="n">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="BF2" t="n">
-        <v>3500000</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="BH2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="BI2" t="n">
-        <v>181.5</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="BK2" t="n">
-        <v>4</v>
+        <v>775000</v>
       </c>
       <c r="BL2" t="n">
-        <v>280</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>15700000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>283</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KdTaErjA</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45490.97916666666</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27000</v>
+        <v>72000</v>
       </c>
       <c r="F3" t="n">
-        <v>19488</v>
+        <v>32905</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -1060,165 +1048,149 @@
       <c r="X3" t="n">
         <v>2024</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
+      <c r="AA3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>178.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.2</v>
+        <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>177.1</v>
+        <v>70.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>3275000</v>
       </c>
       <c r="AF3" t="n">
-        <v>69.5</v>
+        <v>75.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>3882500</v>
+        <v>28.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>74.3</v>
+        <v>181.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.66666666666667</v>
+        <v>1.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>181.1111111111111</v>
+        <v>71.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>4040000</v>
       </c>
       <c r="AL3" t="n">
-        <v>64.77777777777777</v>
+        <v>74.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>1307777.777777778</v>
+        <v>26.05882352941176</v>
       </c>
       <c r="AN3" t="n">
-        <v>70.66666666666667</v>
+        <v>176.0588235294118</v>
       </c>
       <c r="AO3" t="n">
-        <v>26.05555555555556</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AP3" t="n">
-        <v>180.6111111111111</v>
+        <v>66.35294117647059</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.166666666666667</v>
+        <v>2305000</v>
       </c>
       <c r="AR3" t="n">
-        <v>64.05555555555556</v>
+        <v>69.64705882352941</v>
       </c>
       <c r="AS3" t="n">
-        <v>1022222.222222222</v>
+        <v>25.40909090909091</v>
       </c>
       <c r="AT3" t="n">
-        <v>68.05555555555556</v>
+        <v>179.3636363636364</v>
       </c>
       <c r="AU3" t="n">
-        <v>22.39130434782609</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>180.5217391304348</v>
+        <v>66.22727272727273</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1243181.818181818</v>
       </c>
       <c r="AX3" t="n">
-        <v>59.52173913043478</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>609565.2173913043</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>67.82608695652173</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>175</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>73</v>
-      </c>
+        <v>72.59090909090909</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>2900000</v>
+        <v>19</v>
       </c>
       <c r="BG3" t="n">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="BH3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>400000</v>
       </c>
       <c r="BL3" t="n">
-        <v>67</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vaq1CMKM</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45490.97916666666</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18000</v>
+        <v>54405</v>
       </c>
       <c r="F4" t="n">
-        <v>12177</v>
+        <v>24114</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1227,32 +1199,32 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
-        <v>15</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1272,204 +1244,204 @@
       <c r="X4" t="n">
         <v>2024</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
+      <c r="AA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>176.3</v>
+      </c>
       <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2717500</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2095500</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>176.875</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>66.29166666666667</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1518750</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1213750</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AY4" t="n">
         <v>26</v>
       </c>
-      <c r="AD4" t="n">
-        <v>178.6</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2665000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>181.2727272727273</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>68.81818181818181</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2095909.090909091</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>72</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>180.48</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1257800</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>68.56</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>25.73913043478261</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>178.6521739130435</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>64.95652173913044</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>991521.7391304348</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>67.65217391304348</v>
+        <v>185</v>
       </c>
       <c r="BA4" t="n">
-        <v>24.5</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>185.5</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="BD4" t="n">
-        <v>2</v>
+        <v>1300000</v>
       </c>
       <c r="BE4" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="BF4" t="n">
-        <v>1225000</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="BH4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="BI4" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>875000</v>
       </c>
       <c r="BL4" t="n">
-        <v>62</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>875000</v>
-      </c>
-      <c r="BN4" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YLr5BtzT</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45490.97916666666</v>
+        <v>45493.9375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30032</v>
-      </c>
+        <v>18061</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>12</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1484,146 +1456,172 @@
       <c r="X5" t="n">
         <v>2024</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>179.2222222222222</v>
       </c>
       <c r="AC5" t="n">
-        <v>26.375</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>178.125</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1364444.444444444</v>
       </c>
       <c r="AF5" t="n">
-        <v>68.5</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>1696250</v>
+        <v>24.54545454545455</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.625</v>
+        <v>178.7272727272727</v>
       </c>
       <c r="AI5" t="n">
-        <v>25.7</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182.7</v>
+        <v>65.63636363636364</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.2</v>
+        <v>1502727.272727273</v>
       </c>
       <c r="AL5" t="n">
-        <v>67.40000000000001</v>
+        <v>72.45454545454545</v>
       </c>
       <c r="AM5" t="n">
-        <v>2105000</v>
+        <v>21.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>70.8</v>
+        <v>181.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>25.20833333333333</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>177.625</v>
+        <v>57.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.166666666666667</v>
+        <v>503500</v>
       </c>
       <c r="AR5" t="n">
-        <v>67.70833333333333</v>
+        <v>67.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>2492708.333333333</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.66666666666667</v>
+        <v>178.6428571428571</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.19047619047619</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>179.8571428571429</v>
+        <v>66.14285714285714</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>1661428.571428571</v>
       </c>
       <c r="AX5" t="n">
-        <v>62.04761904761905</v>
+        <v>70.42857142857143</v>
       </c>
       <c r="AY5" t="n">
-        <v>1108333.333333333</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>69.76190476190476</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>67</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>204</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rRYfhY72</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45490.97916666666</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54405</v>
+        <v>20738</v>
       </c>
       <c r="F6" t="n">
-        <v>23198</v>
+        <v>20738</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1633,31 +1631,31 @@
         <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1672,206 +1670,206 @@
       <c r="X6" t="n">
         <v>2024</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2i4sdl32</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>180.7</v>
+      </c>
       <c r="AC6" t="n">
-        <v>25.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>176.7</v>
+        <v>65.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>825000</v>
       </c>
       <c r="AF6" t="n">
-        <v>69</v>
+        <v>67.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2850000</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="AH6" t="n">
-        <v>72.3</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>181.5454545454545</v>
+        <v>67.18181818181819</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.090909090909091</v>
+        <v>1602272.727272727</v>
       </c>
       <c r="AL6" t="n">
-        <v>63.81818181818182</v>
+        <v>71.72727272727273</v>
       </c>
       <c r="AM6" t="n">
-        <v>1132727.272727273</v>
+        <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.09090909090909</v>
+        <v>180</v>
       </c>
       <c r="AO6" t="n">
-        <v>25.26086956521739</v>
+        <v>1.117647058823529</v>
       </c>
       <c r="AP6" t="n">
-        <v>177.1739130434783</v>
+        <v>64.82352941176471</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>942352.9411764706</v>
       </c>
       <c r="AR6" t="n">
-        <v>64.52173913043478</v>
+        <v>66.82352941176471</v>
       </c>
       <c r="AS6" t="n">
-        <v>1217391.304347826</v>
+        <v>25.92857142857143</v>
       </c>
       <c r="AT6" t="n">
-        <v>69.08695652173913</v>
+        <v>182.4285714285714</v>
       </c>
       <c r="AU6" t="n">
-        <v>26.26666666666667</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>181.6</v>
+        <v>65.78571428571429</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.066666666666667</v>
+        <v>1938571.428571429</v>
       </c>
       <c r="AX6" t="n">
-        <v>62.6</v>
+        <v>70.35714285714286</v>
       </c>
       <c r="AY6" t="n">
-        <v>890333.3333333334</v>
+        <v>27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>66.59999999999999</v>
+        <v>179</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>15000000</v>
       </c>
       <c r="BE6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>180</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>68</v>
       </c>
-      <c r="BF6" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
       <c r="BK6" t="n">
-        <v>2</v>
+        <v>400000</v>
       </c>
       <c r="BL6" t="n">
-        <v>129</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>137</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YuRmHp6i</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45490.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>19400</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19679</v>
+      </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>49</v>
+      </c>
+      <c r="L7" t="n">
+        <v>51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>41</v>
-      </c>
-      <c r="L7" t="n">
-        <v>59</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>19</v>
+      </c>
+      <c r="R7" t="n">
         <v>9</v>
       </c>
-      <c r="N7" t="n">
-        <v>12</v>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>18</v>
-      </c>
-      <c r="R7" t="n">
-        <v>13</v>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>bFuhdIb3</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1886,208 +1884,202 @@
       <c r="X7" t="n">
         <v>2024</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
+      <c r="AA7" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>181.6363636363636</v>
       </c>
       <c r="AC7" t="n">
-        <v>25.6</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>181.9</v>
+        <v>63.18181818181818</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1103636.363636364</v>
       </c>
       <c r="AF7" t="n">
-        <v>66.09999999999999</v>
+        <v>68.72727272727273</v>
       </c>
       <c r="AG7" t="n">
-        <v>1965000</v>
+        <v>26.9</v>
       </c>
       <c r="AH7" t="n">
-        <v>69.8</v>
+        <v>180.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>27.6</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>181.1</v>
+        <v>69.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.3</v>
+        <v>2652000</v>
       </c>
       <c r="AL7" t="n">
-        <v>67</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AM7" t="n">
-        <v>2347500</v>
+        <v>27.53846153846154</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.59999999999999</v>
+        <v>177.0769230769231</v>
       </c>
       <c r="AO7" t="n">
-        <v>26.47368421052632</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>182.6842105263158</v>
+        <v>67.38461538461539</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>1767307.692307692</v>
       </c>
       <c r="AR7" t="n">
-        <v>63.31578947368421</v>
+        <v>70.53846153846153</v>
       </c>
       <c r="AS7" t="n">
-        <v>1072631.578947368</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>67.31578947368421</v>
+        <v>180</v>
       </c>
       <c r="AU7" t="n">
-        <v>28.45454545454545</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>180.9545454545455</v>
+        <v>65.36363636363636</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.090909090909091</v>
+        <v>1289772.727272727</v>
       </c>
       <c r="AX7" t="n">
-        <v>65.72727272727273</v>
+        <v>68.72727272727273</v>
       </c>
       <c r="AY7" t="n">
-        <v>931136.3636363636</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="AZ7" t="n">
-        <v>67.59090909090909</v>
+        <v>184</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="BB7" t="n">
-        <v>174</v>
+        <v>3</v>
       </c>
       <c r="BC7" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>1520000</v>
       </c>
       <c r="BE7" t="n">
-        <v>344</v>
+        <v>199</v>
       </c>
       <c r="BF7" t="n">
-        <v>25150000</v>
+        <v>24.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>388</v>
+        <v>185.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="BI7" t="n">
-        <v>185</v>
+        <v>2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>1225000</v>
       </c>
       <c r="BL7" t="n">
-        <v>64</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nqViG4Lc</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45490.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">vazquez r 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19400</v>
+        <v>21650</v>
       </c>
       <c r="F8" t="n">
-        <v>19742</v>
+        <v>19876</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -2102,204 +2094,192 @@
       <c r="X8" t="n">
         <v>2024</v>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>28.27272727272727</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>181.5454545454545</v>
+      </c>
       <c r="AC8" t="n">
-        <v>24.63636363636364</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>182.8181818181818</v>
+        <v>67.27272727272727</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1321818.181818182</v>
       </c>
       <c r="AF8" t="n">
-        <v>64.27272727272727</v>
+        <v>69.18181818181819</v>
       </c>
       <c r="AG8" t="n">
-        <v>1171818.181818182</v>
+        <v>25</v>
       </c>
       <c r="AH8" t="n">
-        <v>69.81818181818181</v>
+        <v>181.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>27.7</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>182.6</v>
+        <v>65.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.1</v>
+        <v>1842500</v>
       </c>
       <c r="AL8" t="n">
-        <v>67.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>1357500</v>
+        <v>25.46666666666667</v>
       </c>
       <c r="AN8" t="n">
-        <v>70.2</v>
+        <v>179.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>25.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>176.875</v>
+        <v>61.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>939000</v>
       </c>
       <c r="AR8" t="n">
-        <v>65.5625</v>
+        <v>66.93333333333334</v>
       </c>
       <c r="AS8" t="n">
-        <v>1518750</v>
+        <v>23.13333333333333</v>
       </c>
       <c r="AT8" t="n">
-        <v>70.5</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AU8" t="n">
-        <v>22.10526315789474</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>184.2105263157895</v>
+        <v>59.66666666666666</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>580000</v>
       </c>
       <c r="AX8" t="n">
-        <v>61.94736842105263</v>
+        <v>68</v>
       </c>
       <c r="AY8" t="n">
-        <v>1055263.157894737</v>
+        <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>71.31578947368421</v>
+        <v>181.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>28.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>185.6666666666667</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="BD8" t="n">
-        <v>3</v>
+        <v>2000000</v>
       </c>
       <c r="BE8" t="n">
-        <v>184</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1270000</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>191</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>182</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>192</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>212</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t6UeFOz4</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45490.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>71000</v>
       </c>
       <c r="F9" t="n">
-        <v>29070</v>
+        <v>42601</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>33</v>
+      </c>
+      <c r="L9" t="n">
+        <v>67</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>52</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>EgT3xN3S</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -2315,207 +2295,187 @@
         <v>2024</v>
       </c>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>179</v>
       </c>
       <c r="AC9" t="n">
-        <v>27.72727272727273</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AD9" t="n">
-        <v>183.0909090909091</v>
+        <v>66.72727272727273</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.090909090909091</v>
+        <v>1174090.909090909</v>
       </c>
       <c r="AF9" t="n">
-        <v>67.72727272727273</v>
+        <v>68.90909090909091</v>
       </c>
       <c r="AG9" t="n">
-        <v>2820454.545454545</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>69.18181818181819</v>
+        <v>182</v>
       </c>
       <c r="AI9" t="n">
-        <v>25.8</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>179.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>3570000</v>
       </c>
       <c r="AL9" t="n">
-        <v>69.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>2532500</v>
+        <v>26.46666666666667</v>
       </c>
       <c r="AN9" t="n">
-        <v>72.59999999999999</v>
+        <v>179.0666666666667</v>
       </c>
       <c r="AO9" t="n">
-        <v>25.5</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>181.1</v>
+        <v>66.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1273333.333333333</v>
       </c>
       <c r="AR9" t="n">
-        <v>63.6</v>
+        <v>70.06666666666666</v>
       </c>
       <c r="AS9" t="n">
-        <v>873250</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
-        <v>66.45</v>
+        <v>179.75</v>
       </c>
       <c r="AU9" t="n">
-        <v>26.56521739130435</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>179.8695652173913</v>
+        <v>65.5625</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.391304347826087</v>
+        <v>1309375</v>
       </c>
       <c r="AX9" t="n">
-        <v>66.73913043478261</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3205652.173913043</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>70.82608695652173</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>255</v>
-      </c>
+        <v>71.8125</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>2750000</v>
+        <v>37</v>
       </c>
       <c r="BG9" t="n">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="BH9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="BI9" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>50000</v>
       </c>
       <c r="BL9" t="n">
-        <v>58</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>475000</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>noMTBkUB</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71000</v>
+        <v>23112</v>
       </c>
       <c r="F10" t="n">
-        <v>42524</v>
+        <v>19619</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>57</v>
+      </c>
+      <c r="L10" t="n">
+        <v>43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>40</v>
-      </c>
-      <c r="L10" t="n">
-        <v>60</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="U10" t="n">
@@ -2530,200 +2490,206 @@
       <c r="X10" t="n">
         <v>2024</v>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>179.1818181818182</v>
+      </c>
       <c r="AC10" t="n">
-        <v>28.45454545454545</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AD10" t="n">
-        <v>178</v>
+        <v>66.36363636363636</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.090909090909091</v>
+        <v>1318181.818181818</v>
       </c>
       <c r="AF10" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>27.18181818181818</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>67.54545454545455</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1124090.909090909</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>68.72727272727273</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>21.77777777777778</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>183.7777777777778</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>3235909.090909091</v>
       </c>
       <c r="AL10" t="n">
-        <v>63.66666666666666</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="AM10" t="n">
-        <v>1380555.555555556</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="AN10" t="n">
-        <v>73.22222222222223</v>
+        <v>175.875</v>
       </c>
       <c r="AO10" t="n">
-        <v>24.5</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AP10" t="n">
-        <v>180.0625</v>
+        <v>65.91666666666667</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>1666250</v>
       </c>
       <c r="AR10" t="n">
-        <v>62.625</v>
+        <v>72.58333333333333</v>
       </c>
       <c r="AS10" t="n">
-        <v>739062.5</v>
+        <v>25.14285714285714</v>
       </c>
       <c r="AT10" t="n">
-        <v>69.1875</v>
+        <v>181.3809523809524</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="AV10" t="n">
-        <v>181.8461538461538</v>
+        <v>65</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>1938333.333333333</v>
       </c>
       <c r="AX10" t="n">
-        <v>60.69230769230769</v>
+        <v>69.80952380952381</v>
       </c>
       <c r="AY10" t="n">
-        <v>2115769.230769231</v>
+        <v>26.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>73.76923076923077</v>
+        <v>187</v>
       </c>
       <c r="BA10" t="n">
-        <v>21.25</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>181.75</v>
+        <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>1340000</v>
       </c>
       <c r="BE10" t="n">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="BF10" t="n">
-        <v>6675000</v>
+        <v>23</v>
       </c>
       <c r="BG10" t="n">
-        <v>305</v>
+        <v>181.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>21.4</v>
+        <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>990000</v>
       </c>
       <c r="BL10" t="n">
-        <v>313</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>5995000</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>350</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hpl1gsEp</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20371</v>
+        <v>21550</v>
       </c>
       <c r="F11" t="n">
-        <v>20793</v>
+        <v>20318</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
         <v>9</v>
       </c>
-      <c r="P11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="U11" t="n">
@@ -2738,208 +2704,206 @@
       <c r="X11" t="n">
         <v>2024</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>26.90909090909091</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>183.2727272727273</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.54545454545455</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AD11" t="n">
-        <v>181</v>
+        <v>73.81818181818181</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>6020454.545454546</v>
       </c>
       <c r="AF11" t="n">
-        <v>68.45454545454545</v>
+        <v>77.18181818181819</v>
       </c>
       <c r="AG11" t="n">
-        <v>3663636.363636364</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="AH11" t="n">
-        <v>71.54545454545455</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="AI11" t="n">
-        <v>25.63636363636364</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AJ11" t="n">
-        <v>181.9090909090909</v>
+        <v>68.36363636363636</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>2327272.727272727</v>
       </c>
       <c r="AL11" t="n">
-        <v>66.72727272727273</v>
+        <v>71.36363636363636</v>
       </c>
       <c r="AM11" t="n">
-        <v>1893181.818181818</v>
+        <v>22</v>
       </c>
       <c r="AN11" t="n">
-        <v>71.63636363636364</v>
+        <v>183.3529411764706</v>
       </c>
       <c r="AO11" t="n">
-        <v>23.46153846153846</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>180.6923076923077</v>
+        <v>65.05882352941177</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>1895588.235294118</v>
       </c>
       <c r="AR11" t="n">
-        <v>63.23076923076923</v>
+        <v>74.70588235294117</v>
       </c>
       <c r="AS11" t="n">
-        <v>921538.4615384615</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AT11" t="n">
-        <v>70.76923076923077</v>
+        <v>180.7083333333333</v>
       </c>
       <c r="AU11" t="n">
-        <v>24.47058823529412</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>183.7647058823529</v>
+        <v>62.54166666666666</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>824375</v>
       </c>
       <c r="AX11" t="n">
-        <v>63.11764705882353</v>
+        <v>67.54166666666667</v>
       </c>
       <c r="AY11" t="n">
-        <v>1091764.705882353</v>
+        <v>28.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>68.52941176470588</v>
+        <v>179.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>28.5</v>
+        <v>1.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>179</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="BD11" t="n">
-        <v>2</v>
+        <v>57825000</v>
       </c>
       <c r="BE11" t="n">
-        <v>123</v>
+        <v>384</v>
       </c>
       <c r="BF11" t="n">
-        <v>600000</v>
+        <v>25.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>133</v>
+        <v>177.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>34</v>
+        <v>1.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>8875000</v>
       </c>
       <c r="BL11" t="n">
-        <v>68</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>400000</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>68</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QyLXA9qI</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
+          <t xml:space="preserve">lauziere p 
   can </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>26000</v>
+        <v>68756</v>
       </c>
       <c r="F12" t="n">
-        <v>25513</v>
+        <v>28260</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>17</v>
       </c>
-      <c r="O12" t="n">
-        <v>10</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
       <c r="R12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -2955,158 +2919,152 @@
         <v>2024</v>
       </c>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>183.4444444444445</v>
       </c>
       <c r="AC12" t="n">
-        <v>24.72727272727273</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>180.0909090909091</v>
+        <v>67.44444444444444</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>1222222.222222222</v>
       </c>
       <c r="AF12" t="n">
-        <v>66.09090909090909</v>
+        <v>70</v>
       </c>
       <c r="AG12" t="n">
-        <v>1947272.727272727</v>
+        <v>25.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>70.72727272727273</v>
+        <v>181.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>26.90909090909091</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>183.0909090909091</v>
+        <v>64.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.090909090909091</v>
+        <v>1017500</v>
       </c>
       <c r="AL12" t="n">
-        <v>67.45454545454545</v>
+        <v>68.3</v>
       </c>
       <c r="AM12" t="n">
-        <v>2097727.272727273</v>
+        <v>27</v>
       </c>
       <c r="AN12" t="n">
-        <v>69.63636363636364</v>
+        <v>178.8235294117647</v>
       </c>
       <c r="AO12" t="n">
-        <v>24.08333333333333</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AP12" t="n">
-        <v>183.0416666666667</v>
+        <v>64.82352941176471</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>748529.4117647059</v>
       </c>
       <c r="AR12" t="n">
-        <v>62.83333333333334</v>
+        <v>69.76470588235294</v>
       </c>
       <c r="AS12" t="n">
-        <v>1754583.333333333</v>
+        <v>23.47058823529412</v>
       </c>
       <c r="AT12" t="n">
-        <v>68.25</v>
+        <v>180.6470588235294</v>
       </c>
       <c r="AU12" t="n">
-        <v>24.78260869565218</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>181.2173913043478</v>
+        <v>59.05882352941177</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>437352.9411764706</v>
       </c>
       <c r="AX12" t="n">
-        <v>65.65217391304348</v>
+        <v>66.94117647058823</v>
       </c>
       <c r="AY12" t="n">
-        <v>1732391.304347826</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AZ12" t="n">
-        <v>70.69565217391305</v>
+        <v>177.7142857142857</v>
       </c>
       <c r="BA12" t="n">
-        <v>27.4</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="BB12" t="n">
-        <v>181.4</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>1</v>
+        <v>493</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>34100000</v>
       </c>
       <c r="BE12" t="n">
-        <v>335</v>
+        <v>530</v>
       </c>
       <c r="BF12" t="n">
-        <v>21180000</v>
+        <v>23.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>347</v>
+        <v>178</v>
       </c>
       <c r="BH12" t="n">
-        <v>25.8</v>
+        <v>1.125</v>
       </c>
       <c r="BI12" t="n">
-        <v>177.4</v>
+        <v>8</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.4</v>
+        <v>561</v>
       </c>
       <c r="BK12" t="n">
-        <v>5</v>
+        <v>42350000</v>
       </c>
       <c r="BL12" t="n">
-        <v>337</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>8875000</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>358</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Uoi8UUFe</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F13" t="n">
-        <v>20120</v>
+        <v>19828</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -3116,46 +3074,46 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L13" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>6gpXy3vi</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>CKCtVmJf</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -3171,207 +3129,201 @@
         <v>2024</v>
       </c>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>180.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.7</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>184.2</v>
+        <v>64.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.2</v>
+        <v>1732000</v>
       </c>
       <c r="AF13" t="n">
-        <v>70</v>
+        <v>72.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>3812500</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AH13" t="n">
-        <v>75.5</v>
+        <v>182.3636363636364</v>
       </c>
       <c r="AI13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>179.8</v>
+        <v>64.36363636363636</v>
       </c>
       <c r="AK13" t="n">
+        <v>1640454.545454545</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>180.3125</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1655625</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>25.04166666666667</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>177.2083333333333</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4251875</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>70.41666666666667</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="BA13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL13" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>3539500</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>182.95</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3641250</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>24.20833333333333</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>180.0416666666667</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>64.29166666666667</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1785625</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>68.95833333333333</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>27.66666666666667</v>
-      </c>
       <c r="BB13" t="n">
-        <v>179.1666666666667</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.166666666666667</v>
+        <v>319</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>17800000</v>
       </c>
       <c r="BE13" t="n">
-        <v>456</v>
+        <v>361</v>
       </c>
       <c r="BF13" t="n">
-        <v>72625000</v>
+        <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>474</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="BH13" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="BI13" t="n">
-        <v>181.5</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="BK13" t="n">
-        <v>2</v>
+        <v>2125000</v>
       </c>
       <c r="BL13" t="n">
-        <v>117</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>990000</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>129</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>tMfCTlV1</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="F14" t="n">
-        <v>15128</v>
+        <v>22827</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -3386,141 +3338,139 @@
       <c r="X14" t="n">
         <v>2024</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
+      <c r="AA14" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>178.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.5</v>
+        <v>1.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>180.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2192500</v>
       </c>
       <c r="AF14" t="n">
-        <v>65.7</v>
+        <v>72</v>
       </c>
       <c r="AG14" t="n">
-        <v>1962000</v>
+        <v>22.55555555555556</v>
       </c>
       <c r="AH14" t="n">
-        <v>72.7</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AI14" t="n">
-        <v>24.09090909090909</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>179.8181818181818</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>1555555.555555556</v>
       </c>
       <c r="AL14" t="n">
-        <v>66.45454545454545</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="AM14" t="n">
-        <v>1379545.454545455</v>
+        <v>25.69565217391304</v>
       </c>
       <c r="AN14" t="n">
-        <v>71.27272727272727</v>
+        <v>180.8260869565217</v>
       </c>
       <c r="AO14" t="n">
-        <v>22.0625</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="AP14" t="n">
-        <v>182.0625</v>
+        <v>66.60869565217391</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>3477391.304347826</v>
       </c>
       <c r="AR14" t="n">
-        <v>62.4375</v>
+        <v>71</v>
       </c>
       <c r="AS14" t="n">
-        <v>1271250</v>
+        <v>21.68421052631579</v>
       </c>
       <c r="AT14" t="n">
-        <v>72.5625</v>
+        <v>182.7368421052632</v>
       </c>
       <c r="AU14" t="n">
-        <v>24.58333333333333</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>180.1666666666667</v>
+        <v>63.52631578947368</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.166666666666667</v>
+        <v>1939473.684210526</v>
       </c>
       <c r="AX14" t="n">
-        <v>66.54166666666667</v>
+        <v>72.57894736842105</v>
       </c>
       <c r="AY14" t="n">
-        <v>1595833.333333333</v>
+        <v>20</v>
       </c>
       <c r="AZ14" t="n">
-        <v>71.83333333333333</v>
+        <v>185</v>
       </c>
       <c r="BA14" t="n">
-        <v>22.25</v>
+        <v>1</v>
       </c>
       <c r="BB14" t="n">
-        <v>179.25</v>
+        <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.5</v>
+        <v>58</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>475000</v>
       </c>
       <c r="BE14" t="n">
-        <v>249</v>
+        <v>72</v>
       </c>
       <c r="BF14" t="n">
-        <v>16100000</v>
+        <v>20.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>289</v>
+        <v>180.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="BK14" t="n">
-        <v>2</v>
+        <v>1620000</v>
       </c>
       <c r="BL14" t="n">
-        <v>124</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Wzm5h1Tj</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45490.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
@@ -3534,13 +3484,13 @@
         <v>18500</v>
       </c>
       <c r="F15" t="n">
-        <v>18554</v>
+        <v>18962</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3549,33 +3499,33 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L15" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
+        <v>13</v>
+      </c>
+      <c r="R15" t="n">
         <v>10</v>
       </c>
-      <c r="R15" t="n">
-        <v>6</v>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>6BusaLE3</t>
@@ -3583,7 +3533,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="U15" t="n">
@@ -3598,262 +3548,130 @@
       <c r="X15" t="n">
         <v>2024</v>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>182.4545454545455</v>
+      </c>
       <c r="AC15" t="n">
-        <v>27.72727272727273</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AD15" t="n">
-        <v>183</v>
+        <v>71.27272727272727</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.181818181818182</v>
+        <v>3277272.727272727</v>
       </c>
       <c r="AF15" t="n">
-        <v>72.54545454545455</v>
+        <v>73.72727272727273</v>
       </c>
       <c r="AG15" t="n">
-        <v>3409090.909090909</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AH15" t="n">
-        <v>73.63636363636364</v>
+        <v>182.9090909090909</v>
       </c>
       <c r="AI15" t="n">
-        <v>26.9</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AJ15" t="n">
-        <v>179.8</v>
+        <v>65.72727272727273</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.1</v>
+        <v>2627727.272727273</v>
       </c>
       <c r="AL15" t="n">
-        <v>65.5</v>
+        <v>67.27272727272727</v>
       </c>
       <c r="AM15" t="n">
-        <v>840000</v>
+        <v>26.23809523809524</v>
       </c>
       <c r="AN15" t="n">
-        <v>69.8</v>
+        <v>185.7142857142857</v>
       </c>
       <c r="AO15" t="n">
-        <v>24.41666666666667</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AP15" t="n">
-        <v>181.5833333333333</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.083333333333333</v>
+        <v>1302857.142857143</v>
       </c>
       <c r="AR15" t="n">
-        <v>64.75</v>
+        <v>69.71428571428571</v>
       </c>
       <c r="AS15" t="n">
-        <v>1118333.333333333</v>
+        <v>29.10526315789474</v>
       </c>
       <c r="AT15" t="n">
-        <v>71.5</v>
+        <v>182.421052631579</v>
       </c>
       <c r="AU15" t="n">
-        <v>24.82352941176471</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>182.3529411764706</v>
+        <v>66.10526315789474</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>780263.1578947369</v>
       </c>
       <c r="AX15" t="n">
-        <v>65.35294117647059</v>
+        <v>66.94736842105263</v>
       </c>
       <c r="AY15" t="n">
-        <v>1170588.235294118</v>
+        <v>21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>71.58823529411765</v>
+        <v>175</v>
       </c>
       <c r="BA15" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="BD15" t="n">
-        <v>1</v>
+        <v>275000</v>
       </c>
       <c r="BE15" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="BF15" t="n">
-        <v>275000</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="BG15" t="n">
-        <v>63</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="BH15" t="n">
-        <v>25.5</v>
+        <v>1</v>
       </c>
       <c r="BI15" t="n">
-        <v>173.5</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="BK15" t="n">
-        <v>2</v>
+        <v>1950000</v>
       </c>
       <c r="BL15" t="n">
-        <v>143</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>M9cUJgca</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45490.875</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">meyer b 
-  usa </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">protective stadium
-  birmingham  al </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>47100</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>rysqEtSu</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>EabuZlYo</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>54</v>
-      </c>
-      <c r="L16" t="n">
-        <v>46</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12</v>
-      </c>
-      <c r="N16" t="n">
-        <v>13</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>10</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>v7f8zS64</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>n9nYS6gm</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>167</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1673</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
+        <v>198</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
